--- a/Affectation session  d'automne_2021_2022.xlsx
+++ b/Affectation session  d'automne_2021_2022.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B097C83C-F860-E348-B4D1-3CCBC58E4C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9489BEBB-D317-734D-A6B1-87EFCFC7BB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" tabRatio="630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
